--- a/Digitised_Records_Low_Frequency_2026_05_06.xlsx
+++ b/Digitised_Records_Low_Frequency_2026_05_06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sotonac-my.sharepoint.com/personal/ck1g20_soton_ac_uk/Documents/Documents/PhD/20_Historical_record_catalogue/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_514D7D2F8A27E5EE284527E5E5012D16118664B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1597287F-B7BA-454F-88FF-69ED84E7A0E3}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_514D7D2F8A27E5EE284527E5E5012D16118664B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B21397E0-8279-4A52-8F43-0E73C39F4684}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8378,8 +8378,7 @@
     <col min="5" max="5" width="12.08984375" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.6328125" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.54296875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7265625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="874.1796875" style="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7265625" style="1" customWidth="1"/>
     <col min="10" max="10" width="13.08984375" style="1" customWidth="1"/>
     <col min="11" max="11" width="10.6328125" style="1" customWidth="1"/>
     <col min="12" max="12" width="28" style="1" customWidth="1"/>
@@ -8412,7 +8411,7 @@
       <c r="H1" s="3" t="s">
         <v>2643</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>2644</v>
       </c>
       <c r="J1" s="3" t="s">
